--- a/qiime_mapping/qiime_mapping.xlsx
+++ b/qiime_mapping/qiime_mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pennstateoffice365-my.sharepoint.com/personal/jeh6121_psu_edu/Documents/Documents/Github/BONCAT_mixtures/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pennstateoffice365-my.sharepoint.com/personal/jeh6121_psu_edu/Documents/Documents/Github/BONCAT_mixtures/qiime_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="367" documentId="8_{38C35653-0ED5-46DC-8B17-4733F583B284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{163A503F-D540-42D4-A7A3-490FC8550E80}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="20376" windowHeight="12096" xr2:uid="{14CF2047-F34E-4FAB-8C3A-FAA61A8327C0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="20376" windowHeight="12096" activeTab="1" xr2:uid="{14CF2047-F34E-4FAB-8C3A-FAA61A8327C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="3" r:id="rId1"/>

--- a/qiime_mapping/qiime_mapping.xlsx
+++ b/qiime_mapping/qiime_mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pennstateoffice365-my.sharepoint.com/personal/jeh6121_psu_edu/Documents/Documents/Github/BONCAT_mixtures/qiime_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="367" documentId="8_{38C35653-0ED5-46DC-8B17-4733F583B284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{163A503F-D540-42D4-A7A3-490FC8550E80}"/>
+  <xr:revisionPtr revIDLastSave="372" documentId="8_{38C35653-0ED5-46DC-8B17-4733F583B284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DE5F9D6-28E5-4129-A67F-045AD190EE3C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="20376" windowHeight="12096" activeTab="1" xr2:uid="{14CF2047-F34E-4FAB-8C3A-FAA61A8327C0}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10276" activeTab="1" xr2:uid="{14CF2047-F34E-4FAB-8C3A-FAA61A8327C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="1206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="1203">
   <si>
     <t>BCAT_10_S21_R1_001.fastq.gz</t>
   </si>
@@ -2631,9 +2631,6 @@
     <t>pcr_ctl35_S82</t>
   </si>
   <si>
-    <t>BCAT_10_S21</t>
-  </si>
-  <si>
     <t>BCAT_11_S31</t>
   </si>
   <si>
@@ -2652,1012 +2649,1006 @@
     <t>reverse-absolute-filepath</t>
   </si>
   <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_10_S21_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_11_S31_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_12_S41_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_13_S51_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_14_S61_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_15_S71_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_23_S2_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_24_S12_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_25_S22_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_26_S32_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_27_S42_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_28_S52_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_30_S62_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_38_S72_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_39_S3_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_40_S13_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_41_S23_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_43_S33_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_44_S43_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_45_S53_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_53_S63_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_54_S73_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_55_S4_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_56_S14_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_57_S24_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_59_S44_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_60_S54_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_68_S64_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_69_S74_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_70_S5_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_71_S15_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_72_S25_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_73_S35_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_83_S45_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_84_S55_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_86_S65_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_87_S75_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_88_S6_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_8_S1_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_9_S11_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_10_S97_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_11_S108_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_12_S119_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_13_S130_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_14_S141_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_15_S152_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_16_S163_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_17_S87_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_18_S98_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_19_S109_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_1_S85_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_20_S120_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_21_S131_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_22_S142_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_23_S153_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_24_S164_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_25_S88_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_26_S99_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_27_S110_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_28_S121_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_29_S132_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_2_S96_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_31_S154_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_32_S165_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_33_S89_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_34_S100_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_35_S111_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_36_S122_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_37_S133_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_38_S144_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_39_S155_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_3_S107_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_40_S166_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_41_S90_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_42_S101_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_43_S112_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_44_S123_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_45_S134_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_46_S145_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_47_S156_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_48_S167_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_49_S91_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_4_S118_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_50_S102_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_51_S113_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_52_S124_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_53_S135_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_54_S146_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_55_S157_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_56_S168_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_57_S92_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_58_S103_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_59_S114_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_5_S129_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_60_S125_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_61_S136_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_62_S147_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_63_S158_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_64_S169_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_65_S93_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_66_S104_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_67_S115_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_68_S126_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_69_S137_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_6_S140_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_70_S148_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_71_S159_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_72_S170_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_73_S94_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_74_S105_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_75_S116_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_76_S127_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_77_S138_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_78_S149_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_79_S160_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_7_S151_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_80_S171_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_81_S95_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_82_S106_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_83_S117_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_84_S128_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_85_S139_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_86_S150_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_87_S161_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_88_S172_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_8_S162_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_9_S86_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/fc_ct_iso_S83_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/fc_ct_sh_S84_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_10_S36_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_11_S46_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_12_S56_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_14_S76_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_15_S7_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_23_S17_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_25_S37_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_26_S47_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_27_S57_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_30_S77_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_38_S8_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_39_S18_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_40_S28_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_41_S38_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_43_S48_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_44_S58_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_45_S68_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_53_S78_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_54_S9_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_55_S19_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_56_S29_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_57_S39_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_58_S49_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_59_S59_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_60_S69_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_68_S79_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_69_S10_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_70_S20_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_71_S30_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_72_S40_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_73_S50_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_83_S60_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_84_S70_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_86_S80_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_88_S81_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_8_S16_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_9_S26_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/pcr_ctl25_S173_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/pcr_ctl35_S82_R2_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_10_S21_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_11_S31_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_12_S41_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_13_S51_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_14_S61_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_15_S71_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_23_S2_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_24_S12_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_25_S22_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_26_S32_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_27_S42_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_28_S52_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_30_S62_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_38_S72_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_39_S3_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_40_S13_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_41_S23_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_43_S33_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_44_S43_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_45_S53_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_53_S63_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_54_S73_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_55_S4_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_56_S14_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_57_S24_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_59_S44_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_60_S54_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_68_S64_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_69_S74_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_70_S5_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_71_S15_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_72_S25_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_73_S35_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_83_S45_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_84_S55_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_86_S65_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_87_S75_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_88_S6_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_8_S1_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_9_S11_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_10_S97_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_11_S108_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_12_S119_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_13_S130_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_14_S141_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_15_S152_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_16_S163_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_17_S87_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_18_S98_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_19_S109_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_1_S85_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_20_S120_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_21_S131_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_22_S142_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_23_S153_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_24_S164_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_25_S88_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_26_S99_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_27_S110_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_28_S121_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_29_S132_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_2_S96_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_31_S154_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_32_S165_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_33_S89_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_34_S100_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_35_S111_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_36_S122_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_37_S133_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_38_S144_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_39_S155_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_3_S107_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_40_S166_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_41_S90_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_42_S101_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_43_S112_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_44_S123_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_45_S134_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_46_S145_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_47_S156_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_48_S167_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_49_S91_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_4_S118_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_50_S102_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_51_S113_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_52_S124_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_53_S135_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_54_S146_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_55_S157_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_56_S168_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_57_S92_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_58_S103_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_59_S114_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_5_S129_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_60_S125_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_61_S136_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_62_S147_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_63_S158_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_64_S169_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_65_S93_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_66_S104_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_67_S115_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_68_S126_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_69_S137_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_6_S140_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_70_S148_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_71_S159_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_72_S170_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_73_S94_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_74_S105_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_75_S116_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_76_S127_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_77_S138_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_78_S149_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_79_S160_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_7_S151_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_80_S171_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_81_S95_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_82_S106_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_83_S117_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_84_S128_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_85_S139_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_86_S150_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_87_S161_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_88_S172_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_8_S162_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_9_S86_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/fc_ct_iso_S83_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/fc_ct_sh_S84_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_10_S36_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_11_S46_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_12_S56_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_14_S76_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_15_S7_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_23_S17_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_25_S37_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_26_S47_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_27_S57_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_30_S77_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_38_S8_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_39_S18_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_40_S28_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_41_S38_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_43_S48_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_44_S58_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_45_S68_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_53_S78_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_54_S9_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_55_S19_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_56_S29_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_57_S39_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_58_S49_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_59_S59_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_60_S69_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_68_S79_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_69_S10_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_70_S20_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_71_S30_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_72_S40_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_73_S50_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_83_S60_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_84_S70_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_86_S80_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_88_S81_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_8_S16_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_9_S26_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/pcr_ctl25_S173_R1_001.atria.fastq.gz</t>
-  </si>
-  <si>
-    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/pcr_ctl35_S82_R1_001.atria.fastq.gz</t>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_11_S31_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_12_S41_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_13_S51_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_14_S61_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_15_S71_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_23_S2_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_24_S12_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_25_S22_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_26_S32_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_27_S42_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_28_S52_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_30_S62_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_38_S72_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_39_S3_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_40_S13_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_41_S23_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_43_S33_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_44_S43_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_45_S53_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_53_S63_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_54_S73_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_55_S4_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_56_S14_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_57_S24_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_59_S44_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_60_S54_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_68_S64_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_69_S74_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_70_S5_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_71_S15_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_72_S25_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_73_S35_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_83_S45_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_84_S55_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_86_S65_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_87_S75_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_88_S6_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_8_S1_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_9_S11_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_10_S97_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_11_S108_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_12_S119_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_13_S130_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_14_S141_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_15_S152_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_16_S163_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_17_S87_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_18_S98_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_19_S109_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_1_S85_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_20_S120_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_21_S131_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_22_S142_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_23_S153_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_24_S164_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_25_S88_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_26_S99_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_27_S110_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_28_S121_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_29_S132_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_2_S96_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_31_S154_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_32_S165_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_33_S89_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_34_S100_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_35_S111_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_36_S122_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_37_S133_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_38_S144_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_39_S155_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_3_S107_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_40_S166_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_41_S90_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_42_S101_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_43_S112_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_44_S123_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_45_S134_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_46_S145_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_47_S156_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_48_S167_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_49_S91_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_4_S118_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_50_S102_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_51_S113_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_52_S124_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_53_S135_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_54_S146_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_55_S157_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_56_S168_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_57_S92_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_58_S103_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_59_S114_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_5_S129_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_60_S125_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_61_S136_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_62_S147_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_63_S158_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_64_S169_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_65_S93_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_66_S104_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_67_S115_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_68_S126_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_69_S137_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_6_S140_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_70_S148_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_71_S159_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_72_S170_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_73_S94_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_74_S105_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_75_S116_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_76_S127_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_77_S138_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_78_S149_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_79_S160_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_7_S151_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_80_S171_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_81_S95_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_82_S106_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_83_S117_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_84_S128_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_85_S139_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_86_S150_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_87_S161_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_88_S172_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_8_S162_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_9_S86_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/fc_ct_iso_S83_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/fc_ct_sh_S84_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_10_S36_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_11_S46_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_12_S56_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_14_S76_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_15_S7_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_23_S17_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_25_S37_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_26_S47_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_27_S57_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_30_S77_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_38_S8_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_39_S18_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_40_S28_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_41_S38_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_43_S48_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_44_S58_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_45_S68_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_53_S78_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_54_S9_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_55_S19_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_56_S29_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_57_S39_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_58_S49_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_59_S59_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_60_S69_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_68_S79_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_69_S10_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_70_S20_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_71_S30_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_72_S40_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_73_S50_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_83_S60_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_84_S70_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_86_S80_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_88_S81_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_8_S16_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_9_S26_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/pcr_ctl25_S173_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/pcr_ctl35_S82_R2_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_11_S31_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_12_S41_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_13_S51_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_14_S61_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_15_S71_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_23_S2_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_24_S12_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_25_S22_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_26_S32_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_27_S42_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_28_S52_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_30_S62_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_38_S72_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_39_S3_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_40_S13_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_41_S23_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_43_S33_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_44_S43_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_45_S53_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_53_S63_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_54_S73_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_55_S4_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_56_S14_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_57_S24_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_59_S44_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_60_S54_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_68_S64_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_69_S74_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_70_S5_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_71_S15_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_72_S25_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_73_S35_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_83_S45_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_84_S55_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_86_S65_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_87_S75_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_88_S6_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_8_S1_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/BCAT_9_S11_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_10_S97_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_11_S108_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_12_S119_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_13_S130_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_14_S141_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_15_S152_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_16_S163_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_17_S87_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_18_S98_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_19_S109_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_1_S85_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_20_S120_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_21_S131_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_22_S142_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_23_S153_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_24_S164_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_25_S88_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_26_S99_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_27_S110_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_28_S121_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_29_S132_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_2_S96_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_31_S154_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_32_S165_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_33_S89_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_34_S100_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_35_S111_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_36_S122_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_37_S133_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_38_S144_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_39_S155_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_3_S107_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_40_S166_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_41_S90_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_42_S101_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_43_S112_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_44_S123_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_45_S134_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_46_S145_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_47_S156_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_48_S167_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_49_S91_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_4_S118_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_50_S102_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_51_S113_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_52_S124_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_53_S135_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_54_S146_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_55_S157_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_56_S168_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_57_S92_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_58_S103_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_59_S114_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_5_S129_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_60_S125_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_61_S136_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_62_S147_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_63_S158_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_64_S169_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_65_S93_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_66_S104_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_67_S115_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_68_S126_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_69_S137_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_6_S140_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_70_S148_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_71_S159_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_72_S170_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_73_S94_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_74_S105_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_75_S116_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_76_S127_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_77_S138_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_78_S149_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_79_S160_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_7_S151_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_80_S171_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_81_S95_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_82_S106_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_83_S117_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_84_S128_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_85_S139_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_86_S150_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_87_S161_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_88_S172_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_8_S162_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/T_DNA_9_S86_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/fc_ct_iso_S83_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/fc_ct_sh_S84_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_10_S36_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_11_S46_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_12_S56_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_14_S76_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_15_S7_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_23_S17_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_25_S37_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_26_S47_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_27_S57_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_30_S77_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_38_S8_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_39_S18_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_40_S28_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_41_S38_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_43_S48_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_44_S58_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_45_S68_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_53_S78_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_54_S9_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_55_S19_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_56_S29_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_57_S39_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_58_S49_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_59_S59_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_60_S69_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_68_S79_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_69_S10_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_70_S20_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_71_S30_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_72_S40_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_73_S50_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_83_S60_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_84_S70_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_86_S80_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_88_S81_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_8_S16_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/i_9_S26_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/pcr_ctl25_S173_R1_001.atria.atria.fastq.gz</t>
+  </si>
+  <si>
+    <t>/storage/group/ltb5167/default/JennHarris/Mixtures_BONCAT/16s_seqs/trimmed/pcr_ctl35_S82_R1_001.atria.atria.fastq.gz</t>
   </si>
 </sst>
 </file>
@@ -4030,12 +4021,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42A95D82-9945-419B-9BC5-E7327C0E872E}">
   <dimension ref="A1:C349"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>349</v>
       </c>
@@ -4046,7 +4037,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -4057,7 +4048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -4068,7 +4059,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -4079,7 +4070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -4090,7 +4081,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -4101,7 +4092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -4112,7 +4103,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -4123,7 +4114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -4134,7 +4125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -4145,7 +4136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -4156,7 +4147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -4167,7 +4158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -4178,7 +4169,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>48</v>
       </c>
@@ -4189,7 +4180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>52</v>
       </c>
@@ -4200,7 +4191,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>56</v>
       </c>
@@ -4211,7 +4202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>60</v>
       </c>
@@ -4222,7 +4213,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>64</v>
       </c>
@@ -4233,7 +4224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>68</v>
       </c>
@@ -4244,7 +4235,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>72</v>
       </c>
@@ -4255,7 +4246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>76</v>
       </c>
@@ -4266,7 +4257,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>80</v>
       </c>
@@ -4277,7 +4268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>84</v>
       </c>
@@ -4288,7 +4279,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>88</v>
       </c>
@@ -4299,7 +4290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>92</v>
       </c>
@@ -4310,7 +4301,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>96</v>
       </c>
@@ -4321,7 +4312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>100</v>
       </c>
@@ -4332,7 +4323,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>104</v>
       </c>
@@ -4343,7 +4334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>108</v>
       </c>
@@ -4354,7 +4345,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>112</v>
       </c>
@@ -4365,7 +4356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>116</v>
       </c>
@@ -4376,7 +4367,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>120</v>
       </c>
@@ -4387,7 +4378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>124</v>
       </c>
@@ -4398,7 +4389,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>128</v>
       </c>
@@ -4409,7 +4400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>132</v>
       </c>
@@ -4420,7 +4411,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>136</v>
       </c>
@@ -4431,7 +4422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>140</v>
       </c>
@@ -4442,7 +4433,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>144</v>
       </c>
@@ -4453,7 +4444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>148</v>
       </c>
@@ -4464,7 +4455,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>152</v>
       </c>
@@ -4475,7 +4466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>156</v>
       </c>
@@ -4486,7 +4477,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>160</v>
       </c>
@@ -4497,7 +4488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>164</v>
       </c>
@@ -4508,7 +4499,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>168</v>
       </c>
@@ -4519,7 +4510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>172</v>
       </c>
@@ -4530,7 +4521,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>176</v>
       </c>
@@ -4541,7 +4532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>180</v>
       </c>
@@ -4552,7 +4543,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>184</v>
       </c>
@@ -4563,7 +4554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>188</v>
       </c>
@@ -4574,7 +4565,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>192</v>
       </c>
@@ -4585,7 +4576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>196</v>
       </c>
@@ -4596,7 +4587,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>200</v>
       </c>
@@ -4607,7 +4598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>204</v>
       </c>
@@ -4618,7 +4609,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>208</v>
       </c>
@@ -4629,7 +4620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>212</v>
       </c>
@@ -4640,7 +4631,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>216</v>
       </c>
@@ -4651,7 +4642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>220</v>
       </c>
@@ -4662,7 +4653,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>224</v>
       </c>
@@ -4673,7 +4664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>228</v>
       </c>
@@ -4684,7 +4675,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>232</v>
       </c>
@@ -4695,7 +4686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>236</v>
       </c>
@@ -4706,7 +4697,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>240</v>
       </c>
@@ -4717,7 +4708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>244</v>
       </c>
@@ -4728,7 +4719,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>248</v>
       </c>
@@ -4739,7 +4730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>252</v>
       </c>
@@ -4750,7 +4741,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>256</v>
       </c>
@@ -4761,7 +4752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>260</v>
       </c>
@@ -4772,7 +4763,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>264</v>
       </c>
@@ -4783,7 +4774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>268</v>
       </c>
@@ -4794,7 +4785,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>272</v>
       </c>
@@ -4805,7 +4796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>276</v>
       </c>
@@ -4816,7 +4807,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>280</v>
       </c>
@@ -4827,7 +4818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>284</v>
       </c>
@@ -4838,7 +4829,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>288</v>
       </c>
@@ -4849,7 +4840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>292</v>
       </c>
@@ -4860,7 +4851,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>296</v>
       </c>
@@ -4871,7 +4862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>300</v>
       </c>
@@ -4882,7 +4873,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>304</v>
       </c>
@@ -4893,7 +4884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>308</v>
       </c>
@@ -4904,7 +4895,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>312</v>
       </c>
@@ -4915,7 +4906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>316</v>
       </c>
@@ -4926,7 +4917,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>320</v>
       </c>
@@ -4937,7 +4928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>324</v>
       </c>
@@ -4948,7 +4939,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>328</v>
       </c>
@@ -4959,7 +4950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>332</v>
       </c>
@@ -4970,7 +4961,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>336</v>
       </c>
@@ -4981,7 +4972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>340</v>
       </c>
@@ -4992,7 +4983,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>344</v>
       </c>
@@ -5003,7 +4994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>1</v>
       </c>
@@ -5014,7 +5005,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>5</v>
       </c>
@@ -5025,7 +5016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>9</v>
       </c>
@@ -5036,7 +5027,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>13</v>
       </c>
@@ -5047,7 +5038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>17</v>
       </c>
@@ -5058,7 +5049,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>21</v>
       </c>
@@ -5069,7 +5060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>25</v>
       </c>
@@ -5080,7 +5071,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>29</v>
       </c>
@@ -5091,7 +5082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>33</v>
       </c>
@@ -5102,7 +5093,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>37</v>
       </c>
@@ -5113,7 +5104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>41</v>
       </c>
@@ -5124,7 +5115,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>45</v>
       </c>
@@ -5135,7 +5126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>49</v>
       </c>
@@ -5146,7 +5137,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>53</v>
       </c>
@@ -5157,7 +5148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>57</v>
       </c>
@@ -5168,7 +5159,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>61</v>
       </c>
@@ -5179,7 +5170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>65</v>
       </c>
@@ -5190,7 +5181,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>69</v>
       </c>
@@ -5201,7 +5192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>73</v>
       </c>
@@ -5212,7 +5203,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>77</v>
       </c>
@@ -5223,7 +5214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>81</v>
       </c>
@@ -5234,7 +5225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>85</v>
       </c>
@@ -5245,7 +5236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>89</v>
       </c>
@@ -5256,7 +5247,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>93</v>
       </c>
@@ -5267,7 +5258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>97</v>
       </c>
@@ -5278,7 +5269,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>101</v>
       </c>
@@ -5289,7 +5280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>105</v>
       </c>
@@ -5300,7 +5291,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>109</v>
       </c>
@@ -5311,7 +5302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>113</v>
       </c>
@@ -5322,7 +5313,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>117</v>
       </c>
@@ -5333,7 +5324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>121</v>
       </c>
@@ -5344,7 +5335,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>125</v>
       </c>
@@ -5355,7 +5346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>129</v>
       </c>
@@ -5366,7 +5357,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>133</v>
       </c>
@@ -5377,7 +5368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>137</v>
       </c>
@@ -5388,7 +5379,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>141</v>
       </c>
@@ -5399,7 +5390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>145</v>
       </c>
@@ -5410,7 +5401,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>149</v>
       </c>
@@ -5421,7 +5412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>153</v>
       </c>
@@ -5432,7 +5423,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>157</v>
       </c>
@@ -5443,7 +5434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>161</v>
       </c>
@@ -5454,7 +5445,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>165</v>
       </c>
@@ -5465,7 +5456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>169</v>
       </c>
@@ -5476,7 +5467,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>173</v>
       </c>
@@ -5487,7 +5478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>177</v>
       </c>
@@ -5498,7 +5489,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>181</v>
       </c>
@@ -5509,7 +5500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>185</v>
       </c>
@@ -5520,7 +5511,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>189</v>
       </c>
@@ -5531,7 +5522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>193</v>
       </c>
@@ -5542,7 +5533,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>197</v>
       </c>
@@ -5553,7 +5544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>201</v>
       </c>
@@ -5564,7 +5555,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>205</v>
       </c>
@@ -5575,7 +5566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>209</v>
       </c>
@@ -5586,7 +5577,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>213</v>
       </c>
@@ -5597,7 +5588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>217</v>
       </c>
@@ -5608,7 +5599,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>221</v>
       </c>
@@ -5619,7 +5610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>225</v>
       </c>
@@ -5630,7 +5621,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>229</v>
       </c>
@@ -5641,7 +5632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>233</v>
       </c>
@@ -5652,7 +5643,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>237</v>
       </c>
@@ -5663,7 +5654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>241</v>
       </c>
@@ -5674,7 +5665,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>245</v>
       </c>
@@ -5685,7 +5676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>249</v>
       </c>
@@ -5696,7 +5687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>253</v>
       </c>
@@ -5707,7 +5698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>257</v>
       </c>
@@ -5718,7 +5709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>261</v>
       </c>
@@ -5729,7 +5720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>265</v>
       </c>
@@ -5740,7 +5731,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>269</v>
       </c>
@@ -5751,7 +5742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>273</v>
       </c>
@@ -5762,7 +5753,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>277</v>
       </c>
@@ -5773,7 +5764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>281</v>
       </c>
@@ -5784,7 +5775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>285</v>
       </c>
@@ -5795,7 +5786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>289</v>
       </c>
@@ -5806,7 +5797,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>293</v>
       </c>
@@ -5817,7 +5808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>297</v>
       </c>
@@ -5828,7 +5819,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>301</v>
       </c>
@@ -5839,7 +5830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>305</v>
       </c>
@@ -5850,7 +5841,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>309</v>
       </c>
@@ -5861,7 +5852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>313</v>
       </c>
@@ -5872,7 +5863,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>317</v>
       </c>
@@ -5883,7 +5874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>321</v>
       </c>
@@ -5894,7 +5885,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>325</v>
       </c>
@@ -5905,7 +5896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>329</v>
       </c>
@@ -5916,7 +5907,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>333</v>
       </c>
@@ -5927,7 +5918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>337</v>
       </c>
@@ -5938,7 +5929,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>341</v>
       </c>
@@ -5949,7 +5940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>345</v>
       </c>
@@ -5960,7 +5951,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>2</v>
       </c>
@@ -5971,7 +5962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>6</v>
       </c>
@@ -5982,7 +5973,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>10</v>
       </c>
@@ -5993,7 +5984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>14</v>
       </c>
@@ -6004,7 +5995,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>18</v>
       </c>
@@ -6015,7 +6006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>22</v>
       </c>
@@ -6026,7 +6017,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>26</v>
       </c>
@@ -6037,7 +6028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>30</v>
       </c>
@@ -6048,7 +6039,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>34</v>
       </c>
@@ -6059,7 +6050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>38</v>
       </c>
@@ -6070,7 +6061,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>42</v>
       </c>
@@ -6081,7 +6072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>46</v>
       </c>
@@ -6092,7 +6083,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>50</v>
       </c>
@@ -6103,7 +6094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>54</v>
       </c>
@@ -6114,7 +6105,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>58</v>
       </c>
@@ -6125,7 +6116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>62</v>
       </c>
@@ -6136,7 +6127,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>66</v>
       </c>
@@ -6147,7 +6138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>70</v>
       </c>
@@ -6158,7 +6149,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
         <v>74</v>
       </c>
@@ -6169,7 +6160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
         <v>78</v>
       </c>
@@ -6180,7 +6171,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>82</v>
       </c>
@@ -6191,7 +6182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>86</v>
       </c>
@@ -6202,7 +6193,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
         <v>90</v>
       </c>
@@ -6213,7 +6204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
         <v>94</v>
       </c>
@@ -6224,7 +6215,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
         <v>98</v>
       </c>
@@ -6235,7 +6226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
         <v>102</v>
       </c>
@@ -6246,7 +6237,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
         <v>106</v>
       </c>
@@ -6257,7 +6248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
         <v>110</v>
       </c>
@@ -6268,7 +6259,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
         <v>114</v>
       </c>
@@ -6279,7 +6270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
         <v>118</v>
       </c>
@@ -6290,7 +6281,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
         <v>122</v>
       </c>
@@ -6301,7 +6292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
         <v>126</v>
       </c>
@@ -6312,7 +6303,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
         <v>130</v>
       </c>
@@ -6323,7 +6314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
         <v>134</v>
       </c>
@@ -6334,7 +6325,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
         <v>138</v>
       </c>
@@ -6345,7 +6336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
         <v>142</v>
       </c>
@@ -6356,7 +6347,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
         <v>146</v>
       </c>
@@ -6367,7 +6358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
         <v>150</v>
       </c>
@@ -6378,7 +6369,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
         <v>154</v>
       </c>
@@ -6389,7 +6380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
         <v>158</v>
       </c>
@@ -6400,7 +6391,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
         <v>162</v>
       </c>
@@ -6411,7 +6402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
         <v>166</v>
       </c>
@@ -6422,7 +6413,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
         <v>170</v>
       </c>
@@ -6433,7 +6424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
         <v>174</v>
       </c>
@@ -6444,7 +6435,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
         <v>178</v>
       </c>
@@ -6455,7 +6446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
         <v>182</v>
       </c>
@@ -6466,7 +6457,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
         <v>186</v>
       </c>
@@ -6477,7 +6468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
         <v>190</v>
       </c>
@@ -6488,7 +6479,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
         <v>194</v>
       </c>
@@ -6499,7 +6490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
         <v>198</v>
       </c>
@@ -6510,7 +6501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
         <v>202</v>
       </c>
@@ -6521,7 +6512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A227" t="s">
         <v>206</v>
       </c>
@@ -6532,7 +6523,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
         <v>210</v>
       </c>
@@ -6543,7 +6534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
         <v>214</v>
       </c>
@@ -6554,7 +6545,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
         <v>218</v>
       </c>
@@ -6565,7 +6556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A231" t="s">
         <v>222</v>
       </c>
@@ -6576,7 +6567,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A232" t="s">
         <v>226</v>
       </c>
@@ -6587,7 +6578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
         <v>230</v>
       </c>
@@ -6598,7 +6589,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A234" t="s">
         <v>234</v>
       </c>
@@ -6609,7 +6600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
         <v>238</v>
       </c>
@@ -6620,7 +6611,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A236" t="s">
         <v>242</v>
       </c>
@@ -6631,7 +6622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A237" t="s">
         <v>246</v>
       </c>
@@ -6642,7 +6633,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A238" t="s">
         <v>250</v>
       </c>
@@ -6653,7 +6644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A239" t="s">
         <v>254</v>
       </c>
@@ -6664,7 +6655,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A240" t="s">
         <v>258</v>
       </c>
@@ -6675,7 +6666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
         <v>262</v>
       </c>
@@ -6686,7 +6677,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
         <v>266</v>
       </c>
@@ -6697,7 +6688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A243" t="s">
         <v>270</v>
       </c>
@@ -6708,7 +6699,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
         <v>274</v>
       </c>
@@ -6719,7 +6710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A245" t="s">
         <v>278</v>
       </c>
@@ -6730,7 +6721,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A246" t="s">
         <v>282</v>
       </c>
@@ -6741,7 +6732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A247" t="s">
         <v>286</v>
       </c>
@@ -6752,7 +6743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
         <v>290</v>
       </c>
@@ -6763,7 +6754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
         <v>294</v>
       </c>
@@ -6774,7 +6765,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
         <v>298</v>
       </c>
@@ -6785,7 +6776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
         <v>302</v>
       </c>
@@ -6796,7 +6787,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
         <v>306</v>
       </c>
@@ -6807,7 +6798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
         <v>310</v>
       </c>
@@ -6818,7 +6809,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A254" t="s">
         <v>314</v>
       </c>
@@ -6829,7 +6820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A255" t="s">
         <v>318</v>
       </c>
@@ -6840,7 +6831,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A256" t="s">
         <v>322</v>
       </c>
@@ -6851,7 +6842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
         <v>326</v>
       </c>
@@ -6862,7 +6853,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A258" t="s">
         <v>330</v>
       </c>
@@ -6873,7 +6864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
         <v>334</v>
       </c>
@@ -6884,7 +6875,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A260" t="s">
         <v>338</v>
       </c>
@@ -6895,7 +6886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A261" t="s">
         <v>342</v>
       </c>
@@ -6906,7 +6897,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
         <v>346</v>
       </c>
@@ -6917,7 +6908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A263" t="s">
         <v>3</v>
       </c>
@@ -6928,7 +6919,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A264" t="s">
         <v>7</v>
       </c>
@@ -6939,7 +6930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
         <v>11</v>
       </c>
@@ -6950,7 +6941,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A266" t="s">
         <v>15</v>
       </c>
@@ -6961,7 +6952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A267" t="s">
         <v>19</v>
       </c>
@@ -6972,7 +6963,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
         <v>23</v>
       </c>
@@ -6983,7 +6974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A269" t="s">
         <v>27</v>
       </c>
@@ -6994,7 +6985,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A270" t="s">
         <v>31</v>
       </c>
@@ -7005,7 +6996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
         <v>35</v>
       </c>
@@ -7016,7 +7007,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A272" t="s">
         <v>39</v>
       </c>
@@ -7027,7 +7018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
         <v>43</v>
       </c>
@@ -7038,7 +7029,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A274" t="s">
         <v>47</v>
       </c>
@@ -7049,7 +7040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A275" t="s">
         <v>51</v>
       </c>
@@ -7060,7 +7051,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A276" t="s">
         <v>55</v>
       </c>
@@ -7071,7 +7062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
         <v>59</v>
       </c>
@@ -7082,7 +7073,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A278" t="s">
         <v>63</v>
       </c>
@@ -7093,7 +7084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A279" t="s">
         <v>67</v>
       </c>
@@ -7104,7 +7095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
         <v>71</v>
       </c>
@@ -7115,7 +7106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A281" t="s">
         <v>75</v>
       </c>
@@ -7126,7 +7117,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A282" t="s">
         <v>79</v>
       </c>
@@ -7137,7 +7128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A283" t="s">
         <v>83</v>
       </c>
@@ -7148,7 +7139,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A284" t="s">
         <v>87</v>
       </c>
@@ -7159,7 +7150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A285" t="s">
         <v>91</v>
       </c>
@@ -7170,7 +7161,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A286" t="s">
         <v>95</v>
       </c>
@@ -7181,7 +7172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A287" t="s">
         <v>99</v>
       </c>
@@ -7192,7 +7183,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A288" t="s">
         <v>103</v>
       </c>
@@ -7203,7 +7194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
         <v>107</v>
       </c>
@@ -7214,7 +7205,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A290" t="s">
         <v>111</v>
       </c>
@@ -7225,7 +7216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A291" t="s">
         <v>115</v>
       </c>
@@ -7236,7 +7227,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A292" t="s">
         <v>119</v>
       </c>
@@ -7247,7 +7238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A293" t="s">
         <v>123</v>
       </c>
@@ -7258,7 +7249,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A294" t="s">
         <v>127</v>
       </c>
@@ -7269,7 +7260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A295" t="s">
         <v>131</v>
       </c>
@@ -7280,7 +7271,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A296" t="s">
         <v>135</v>
       </c>
@@ -7291,7 +7282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A297" t="s">
         <v>139</v>
       </c>
@@ -7302,7 +7293,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
         <v>143</v>
       </c>
@@ -7313,7 +7304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A299" t="s">
         <v>147</v>
       </c>
@@ -7324,7 +7315,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A300" t="s">
         <v>151</v>
       </c>
@@ -7335,7 +7326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A301" t="s">
         <v>155</v>
       </c>
@@ -7346,7 +7337,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A302" t="s">
         <v>159</v>
       </c>
@@ -7357,7 +7348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A303" t="s">
         <v>163</v>
       </c>
@@ -7368,7 +7359,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A304" t="s">
         <v>167</v>
       </c>
@@ -7379,7 +7370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A305" t="s">
         <v>171</v>
       </c>
@@ -7390,7 +7381,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A306" t="s">
         <v>175</v>
       </c>
@@ -7401,7 +7392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
         <v>179</v>
       </c>
@@ -7412,7 +7403,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A308" t="s">
         <v>183</v>
       </c>
@@ -7423,7 +7414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A309" t="s">
         <v>187</v>
       </c>
@@ -7434,7 +7425,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A310" t="s">
         <v>191</v>
       </c>
@@ -7445,7 +7436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A311" t="s">
         <v>195</v>
       </c>
@@ -7456,7 +7447,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A312" t="s">
         <v>199</v>
       </c>
@@ -7467,7 +7458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
         <v>203</v>
       </c>
@@ -7478,7 +7469,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A314" t="s">
         <v>207</v>
       </c>
@@ -7489,7 +7480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A315" t="s">
         <v>211</v>
       </c>
@@ -7500,7 +7491,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
         <v>215</v>
       </c>
@@ -7511,7 +7502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A317" t="s">
         <v>219</v>
       </c>
@@ -7522,7 +7513,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A318" t="s">
         <v>223</v>
       </c>
@@ -7533,7 +7524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A319" t="s">
         <v>227</v>
       </c>
@@ -7544,7 +7535,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A320" t="s">
         <v>231</v>
       </c>
@@ -7555,7 +7546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A321" t="s">
         <v>235</v>
       </c>
@@ -7566,7 +7557,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A322" t="s">
         <v>239</v>
       </c>
@@ -7577,7 +7568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A323" t="s">
         <v>243</v>
       </c>
@@ -7588,7 +7579,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A324" t="s">
         <v>247</v>
       </c>
@@ -7599,7 +7590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
         <v>251</v>
       </c>
@@ -7610,7 +7601,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A326" t="s">
         <v>255</v>
       </c>
@@ -7621,7 +7612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A327" t="s">
         <v>259</v>
       </c>
@@ -7632,7 +7623,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A328" t="s">
         <v>263</v>
       </c>
@@ -7643,7 +7634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A329" t="s">
         <v>267</v>
       </c>
@@ -7654,7 +7645,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A330" t="s">
         <v>271</v>
       </c>
@@ -7665,7 +7656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
         <v>275</v>
       </c>
@@ -7676,7 +7667,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A332" t="s">
         <v>279</v>
       </c>
@@ -7687,7 +7678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A333" t="s">
         <v>283</v>
       </c>
@@ -7698,7 +7689,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A334" t="s">
         <v>287</v>
       </c>
@@ -7709,7 +7700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A335" t="s">
         <v>291</v>
       </c>
@@ -7720,7 +7711,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A336" t="s">
         <v>295</v>
       </c>
@@ -7731,7 +7722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A337" t="s">
         <v>299</v>
       </c>
@@ -7742,7 +7733,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A338" t="s">
         <v>303</v>
       </c>
@@ -7753,7 +7744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A339" t="s">
         <v>307</v>
       </c>
@@ -7764,7 +7755,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A340" t="s">
         <v>311</v>
       </c>
@@ -7775,7 +7766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A341" t="s">
         <v>315</v>
       </c>
@@ -7786,7 +7777,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A342" t="s">
         <v>319</v>
       </c>
@@ -7797,7 +7788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
         <v>323</v>
       </c>
@@ -7808,7 +7799,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A344" t="s">
         <v>327</v>
       </c>
@@ -7819,7 +7810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A345" t="s">
         <v>331</v>
       </c>
@@ -7830,7 +7821,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A346" t="s">
         <v>335</v>
       </c>
@@ -7841,7 +7832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A347" t="s">
         <v>339</v>
       </c>
@@ -7852,7 +7843,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A348" t="s">
         <v>343</v>
       </c>
@@ -7863,7 +7854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A349" t="s">
         <v>347</v>
       </c>
@@ -7882,1871 +7873,1860 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{663BA43C-9887-4C2C-A688-4FDB3E97EE39}">
-  <dimension ref="A1:C169"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C168"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="26.21875" customWidth="1"/>
-    <col min="2" max="2" width="17.33203125" customWidth="1"/>
-    <col min="3" max="3" width="15.21875" customWidth="1"/>
+    <col min="1" max="1" width="26.19921875" customWidth="1"/>
+    <col min="2" max="2" width="98.19921875" customWidth="1"/>
+    <col min="3" max="3" width="15.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>866</v>
+      </c>
+      <c r="B1" t="s">
         <v>867</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>868</v>
       </c>
-      <c r="C1" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>863</v>
       </c>
       <c r="B2" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C2" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>864</v>
       </c>
       <c r="B3" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C3" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>865</v>
       </c>
       <c r="B4" t="s">
+        <v>871</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>699</v>
+      </c>
+      <c r="B5" t="s">
         <v>872</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>700</v>
+      </c>
+      <c r="B6" t="s">
+        <v>873</v>
+      </c>
+      <c r="C6" t="s">
         <v>1040</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>866</v>
-      </c>
-      <c r="B5" t="s">
-        <v>873</v>
-      </c>
-      <c r="C5" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>701</v>
+      </c>
+      <c r="B7" t="s">
+        <v>874</v>
+      </c>
+      <c r="C7" t="s">
         <v>1041</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>699</v>
-      </c>
-      <c r="B6" t="s">
-        <v>874</v>
-      </c>
-      <c r="C6" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>702</v>
+      </c>
+      <c r="B8" t="s">
+        <v>875</v>
+      </c>
+      <c r="C8" t="s">
         <v>1042</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>700</v>
-      </c>
-      <c r="B7" t="s">
-        <v>875</v>
-      </c>
-      <c r="C7" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>703</v>
+      </c>
+      <c r="B9" t="s">
+        <v>876</v>
+      </c>
+      <c r="C9" t="s">
         <v>1043</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>701</v>
-      </c>
-      <c r="B8" t="s">
-        <v>876</v>
-      </c>
-      <c r="C8" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>704</v>
+      </c>
+      <c r="B10" t="s">
+        <v>877</v>
+      </c>
+      <c r="C10" t="s">
         <v>1044</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>702</v>
-      </c>
-      <c r="B9" t="s">
-        <v>877</v>
-      </c>
-      <c r="C9" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>705</v>
+      </c>
+      <c r="B11" t="s">
+        <v>878</v>
+      </c>
+      <c r="C11" t="s">
         <v>1045</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>703</v>
-      </c>
-      <c r="B10" t="s">
-        <v>878</v>
-      </c>
-      <c r="C10" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>706</v>
+      </c>
+      <c r="B12" t="s">
+        <v>879</v>
+      </c>
+      <c r="C12" t="s">
         <v>1046</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>704</v>
-      </c>
-      <c r="B11" t="s">
-        <v>879</v>
-      </c>
-      <c r="C11" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>707</v>
+      </c>
+      <c r="B13" t="s">
+        <v>880</v>
+      </c>
+      <c r="C13" t="s">
         <v>1047</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>705</v>
-      </c>
-      <c r="B12" t="s">
-        <v>880</v>
-      </c>
-      <c r="C12" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>708</v>
+      </c>
+      <c r="B14" t="s">
+        <v>881</v>
+      </c>
+      <c r="C14" t="s">
         <v>1048</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>706</v>
-      </c>
-      <c r="B13" t="s">
-        <v>881</v>
-      </c>
-      <c r="C13" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>709</v>
+      </c>
+      <c r="B15" t="s">
+        <v>882</v>
+      </c>
+      <c r="C15" t="s">
         <v>1049</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>707</v>
-      </c>
-      <c r="B14" t="s">
-        <v>882</v>
-      </c>
-      <c r="C14" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>710</v>
+      </c>
+      <c r="B16" t="s">
+        <v>883</v>
+      </c>
+      <c r="C16" t="s">
         <v>1050</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>708</v>
-      </c>
-      <c r="B15" t="s">
-        <v>883</v>
-      </c>
-      <c r="C15" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>711</v>
+      </c>
+      <c r="B17" t="s">
+        <v>884</v>
+      </c>
+      <c r="C17" t="s">
         <v>1051</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>709</v>
-      </c>
-      <c r="B16" t="s">
-        <v>884</v>
-      </c>
-      <c r="C16" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>712</v>
+      </c>
+      <c r="B18" t="s">
+        <v>885</v>
+      </c>
+      <c r="C18" t="s">
         <v>1052</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>710</v>
-      </c>
-      <c r="B17" t="s">
-        <v>885</v>
-      </c>
-      <c r="C17" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>713</v>
+      </c>
+      <c r="B19" t="s">
+        <v>886</v>
+      </c>
+      <c r="C19" t="s">
         <v>1053</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>711</v>
-      </c>
-      <c r="B18" t="s">
-        <v>886</v>
-      </c>
-      <c r="C18" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>714</v>
+      </c>
+      <c r="B20" t="s">
+        <v>887</v>
+      </c>
+      <c r="C20" t="s">
         <v>1054</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>712</v>
-      </c>
-      <c r="B19" t="s">
-        <v>887</v>
-      </c>
-      <c r="C19" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>715</v>
+      </c>
+      <c r="B21" t="s">
+        <v>888</v>
+      </c>
+      <c r="C21" t="s">
         <v>1055</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>713</v>
-      </c>
-      <c r="B20" t="s">
-        <v>888</v>
-      </c>
-      <c r="C20" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>716</v>
+      </c>
+      <c r="B22" t="s">
+        <v>889</v>
+      </c>
+      <c r="C22" t="s">
         <v>1056</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>714</v>
-      </c>
-      <c r="B21" t="s">
-        <v>889</v>
-      </c>
-      <c r="C21" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>717</v>
+      </c>
+      <c r="B23" t="s">
+        <v>890</v>
+      </c>
+      <c r="C23" t="s">
         <v>1057</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>715</v>
-      </c>
-      <c r="B22" t="s">
-        <v>890</v>
-      </c>
-      <c r="C22" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>718</v>
+      </c>
+      <c r="B24" t="s">
+        <v>891</v>
+      </c>
+      <c r="C24" t="s">
         <v>1058</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>716</v>
-      </c>
-      <c r="B23" t="s">
-        <v>891</v>
-      </c>
-      <c r="C23" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>719</v>
+      </c>
+      <c r="B25" t="s">
+        <v>892</v>
+      </c>
+      <c r="C25" t="s">
         <v>1059</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>717</v>
-      </c>
-      <c r="B24" t="s">
-        <v>892</v>
-      </c>
-      <c r="C24" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>720</v>
+      </c>
+      <c r="B26" t="s">
+        <v>893</v>
+      </c>
+      <c r="C26" t="s">
         <v>1060</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>718</v>
-      </c>
-      <c r="B25" t="s">
-        <v>893</v>
-      </c>
-      <c r="C25" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>721</v>
+      </c>
+      <c r="B27" t="s">
+        <v>894</v>
+      </c>
+      <c r="C27" t="s">
         <v>1061</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>719</v>
-      </c>
-      <c r="B26" t="s">
-        <v>894</v>
-      </c>
-      <c r="C26" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>722</v>
+      </c>
+      <c r="B28" t="s">
+        <v>895</v>
+      </c>
+      <c r="C28" t="s">
         <v>1062</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>720</v>
-      </c>
-      <c r="B27" t="s">
-        <v>895</v>
-      </c>
-      <c r="C27" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>723</v>
+      </c>
+      <c r="B29" t="s">
+        <v>896</v>
+      </c>
+      <c r="C29" t="s">
         <v>1063</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>721</v>
-      </c>
-      <c r="B28" t="s">
-        <v>896</v>
-      </c>
-      <c r="C28" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>724</v>
+      </c>
+      <c r="B30" t="s">
+        <v>897</v>
+      </c>
+      <c r="C30" t="s">
         <v>1064</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>722</v>
-      </c>
-      <c r="B29" t="s">
-        <v>897</v>
-      </c>
-      <c r="C29" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>725</v>
+      </c>
+      <c r="B31" t="s">
+        <v>898</v>
+      </c>
+      <c r="C31" t="s">
         <v>1065</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>723</v>
-      </c>
-      <c r="B30" t="s">
-        <v>898</v>
-      </c>
-      <c r="C30" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>726</v>
+      </c>
+      <c r="B32" t="s">
+        <v>899</v>
+      </c>
+      <c r="C32" t="s">
         <v>1066</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>724</v>
-      </c>
-      <c r="B31" t="s">
-        <v>899</v>
-      </c>
-      <c r="C31" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>727</v>
+      </c>
+      <c r="B33" t="s">
+        <v>900</v>
+      </c>
+      <c r="C33" t="s">
         <v>1067</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>725</v>
-      </c>
-      <c r="B32" t="s">
-        <v>900</v>
-      </c>
-      <c r="C32" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>728</v>
+      </c>
+      <c r="B34" t="s">
+        <v>901</v>
+      </c>
+      <c r="C34" t="s">
         <v>1068</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>726</v>
-      </c>
-      <c r="B33" t="s">
-        <v>901</v>
-      </c>
-      <c r="C33" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>729</v>
+      </c>
+      <c r="B35" t="s">
+        <v>902</v>
+      </c>
+      <c r="C35" t="s">
         <v>1069</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>727</v>
-      </c>
-      <c r="B34" t="s">
-        <v>902</v>
-      </c>
-      <c r="C34" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>730</v>
+      </c>
+      <c r="B36" t="s">
+        <v>903</v>
+      </c>
+      <c r="C36" t="s">
         <v>1070</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>728</v>
-      </c>
-      <c r="B35" t="s">
-        <v>903</v>
-      </c>
-      <c r="C35" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>731</v>
+      </c>
+      <c r="B37" t="s">
+        <v>904</v>
+      </c>
+      <c r="C37" t="s">
         <v>1071</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>729</v>
-      </c>
-      <c r="B36" t="s">
-        <v>904</v>
-      </c>
-      <c r="C36" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>732</v>
+      </c>
+      <c r="B38" t="s">
+        <v>905</v>
+      </c>
+      <c r="C38" t="s">
         <v>1072</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>730</v>
-      </c>
-      <c r="B37" t="s">
-        <v>905</v>
-      </c>
-      <c r="C37" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>733</v>
+      </c>
+      <c r="B39" t="s">
+        <v>906</v>
+      </c>
+      <c r="C39" t="s">
         <v>1073</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>731</v>
-      </c>
-      <c r="B38" t="s">
-        <v>906</v>
-      </c>
-      <c r="C38" t="s">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>734</v>
+      </c>
+      <c r="B40" t="s">
+        <v>907</v>
+      </c>
+      <c r="C40" t="s">
         <v>1074</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>732</v>
-      </c>
-      <c r="B39" t="s">
-        <v>907</v>
-      </c>
-      <c r="C39" t="s">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>735</v>
+      </c>
+      <c r="B41" t="s">
+        <v>908</v>
+      </c>
+      <c r="C41" t="s">
         <v>1075</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>733</v>
-      </c>
-      <c r="B40" t="s">
-        <v>908</v>
-      </c>
-      <c r="C40" t="s">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>736</v>
+      </c>
+      <c r="B42" t="s">
+        <v>909</v>
+      </c>
+      <c r="C42" t="s">
         <v>1076</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>734</v>
-      </c>
-      <c r="B41" t="s">
-        <v>909</v>
-      </c>
-      <c r="C41" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>737</v>
+      </c>
+      <c r="B43" t="s">
+        <v>910</v>
+      </c>
+      <c r="C43" t="s">
         <v>1077</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>735</v>
-      </c>
-      <c r="B42" t="s">
-        <v>910</v>
-      </c>
-      <c r="C42" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>738</v>
+      </c>
+      <c r="B44" t="s">
+        <v>911</v>
+      </c>
+      <c r="C44" t="s">
         <v>1078</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>736</v>
-      </c>
-      <c r="B43" t="s">
-        <v>911</v>
-      </c>
-      <c r="C43" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>739</v>
+      </c>
+      <c r="B45" t="s">
+        <v>912</v>
+      </c>
+      <c r="C45" t="s">
         <v>1079</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>737</v>
-      </c>
-      <c r="B44" t="s">
-        <v>912</v>
-      </c>
-      <c r="C44" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>740</v>
+      </c>
+      <c r="B46" t="s">
+        <v>913</v>
+      </c>
+      <c r="C46" t="s">
         <v>1080</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>738</v>
-      </c>
-      <c r="B45" t="s">
-        <v>913</v>
-      </c>
-      <c r="C45" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>741</v>
+      </c>
+      <c r="B47" t="s">
+        <v>914</v>
+      </c>
+      <c r="C47" t="s">
         <v>1081</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>739</v>
-      </c>
-      <c r="B46" t="s">
-        <v>914</v>
-      </c>
-      <c r="C46" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>742</v>
+      </c>
+      <c r="B48" t="s">
+        <v>915</v>
+      </c>
+      <c r="C48" t="s">
         <v>1082</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>740</v>
-      </c>
-      <c r="B47" t="s">
-        <v>915</v>
-      </c>
-      <c r="C47" t="s">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>743</v>
+      </c>
+      <c r="B49" t="s">
+        <v>916</v>
+      </c>
+      <c r="C49" t="s">
         <v>1083</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>741</v>
-      </c>
-      <c r="B48" t="s">
-        <v>916</v>
-      </c>
-      <c r="C48" t="s">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>744</v>
+      </c>
+      <c r="B50" t="s">
+        <v>917</v>
+      </c>
+      <c r="C50" t="s">
         <v>1084</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>742</v>
-      </c>
-      <c r="B49" t="s">
-        <v>917</v>
-      </c>
-      <c r="C49" t="s">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>745</v>
+      </c>
+      <c r="B51" t="s">
+        <v>918</v>
+      </c>
+      <c r="C51" t="s">
         <v>1085</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>743</v>
-      </c>
-      <c r="B50" t="s">
-        <v>918</v>
-      </c>
-      <c r="C50" t="s">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>746</v>
+      </c>
+      <c r="B52" t="s">
+        <v>919</v>
+      </c>
+      <c r="C52" t="s">
         <v>1086</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>744</v>
-      </c>
-      <c r="B51" t="s">
-        <v>919</v>
-      </c>
-      <c r="C51" t="s">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>747</v>
+      </c>
+      <c r="B53" t="s">
+        <v>920</v>
+      </c>
+      <c r="C53" t="s">
         <v>1087</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>745</v>
-      </c>
-      <c r="B52" t="s">
-        <v>920</v>
-      </c>
-      <c r="C52" t="s">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>748</v>
+      </c>
+      <c r="B54" t="s">
+        <v>921</v>
+      </c>
+      <c r="C54" t="s">
         <v>1088</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>746</v>
-      </c>
-      <c r="B53" t="s">
-        <v>921</v>
-      </c>
-      <c r="C53" t="s">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>749</v>
+      </c>
+      <c r="B55" t="s">
+        <v>922</v>
+      </c>
+      <c r="C55" t="s">
         <v>1089</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>747</v>
-      </c>
-      <c r="B54" t="s">
-        <v>922</v>
-      </c>
-      <c r="C54" t="s">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>750</v>
+      </c>
+      <c r="B56" t="s">
+        <v>923</v>
+      </c>
+      <c r="C56" t="s">
         <v>1090</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>748</v>
-      </c>
-      <c r="B55" t="s">
-        <v>923</v>
-      </c>
-      <c r="C55" t="s">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>751</v>
+      </c>
+      <c r="B57" t="s">
+        <v>924</v>
+      </c>
+      <c r="C57" t="s">
         <v>1091</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>749</v>
-      </c>
-      <c r="B56" t="s">
-        <v>924</v>
-      </c>
-      <c r="C56" t="s">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>752</v>
+      </c>
+      <c r="B58" t="s">
+        <v>925</v>
+      </c>
+      <c r="C58" t="s">
         <v>1092</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>750</v>
-      </c>
-      <c r="B57" t="s">
-        <v>925</v>
-      </c>
-      <c r="C57" t="s">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>753</v>
+      </c>
+      <c r="B59" t="s">
+        <v>926</v>
+      </c>
+      <c r="C59" t="s">
         <v>1093</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>751</v>
-      </c>
-      <c r="B58" t="s">
-        <v>926</v>
-      </c>
-      <c r="C58" t="s">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>754</v>
+      </c>
+      <c r="B60" t="s">
+        <v>927</v>
+      </c>
+      <c r="C60" t="s">
         <v>1094</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>752</v>
-      </c>
-      <c r="B59" t="s">
-        <v>927</v>
-      </c>
-      <c r="C59" t="s">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>755</v>
+      </c>
+      <c r="B61" t="s">
+        <v>928</v>
+      </c>
+      <c r="C61" t="s">
         <v>1095</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>753</v>
-      </c>
-      <c r="B60" t="s">
-        <v>928</v>
-      </c>
-      <c r="C60" t="s">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>756</v>
+      </c>
+      <c r="B62" t="s">
+        <v>929</v>
+      </c>
+      <c r="C62" t="s">
         <v>1096</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>754</v>
-      </c>
-      <c r="B61" t="s">
-        <v>929</v>
-      </c>
-      <c r="C61" t="s">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>757</v>
+      </c>
+      <c r="B63" t="s">
+        <v>930</v>
+      </c>
+      <c r="C63" t="s">
         <v>1097</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>755</v>
-      </c>
-      <c r="B62" t="s">
-        <v>930</v>
-      </c>
-      <c r="C62" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>758</v>
+      </c>
+      <c r="B64" t="s">
+        <v>931</v>
+      </c>
+      <c r="C64" t="s">
         <v>1098</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>756</v>
-      </c>
-      <c r="B63" t="s">
-        <v>931</v>
-      </c>
-      <c r="C63" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>759</v>
+      </c>
+      <c r="B65" t="s">
+        <v>932</v>
+      </c>
+      <c r="C65" t="s">
         <v>1099</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>757</v>
-      </c>
-      <c r="B64" t="s">
-        <v>932</v>
-      </c>
-      <c r="C64" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>760</v>
+      </c>
+      <c r="B66" t="s">
+        <v>933</v>
+      </c>
+      <c r="C66" t="s">
         <v>1100</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>758</v>
-      </c>
-      <c r="B65" t="s">
-        <v>933</v>
-      </c>
-      <c r="C65" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>761</v>
+      </c>
+      <c r="B67" t="s">
+        <v>934</v>
+      </c>
+      <c r="C67" t="s">
         <v>1101</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>759</v>
-      </c>
-      <c r="B66" t="s">
-        <v>934</v>
-      </c>
-      <c r="C66" t="s">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>762</v>
+      </c>
+      <c r="B68" t="s">
+        <v>935</v>
+      </c>
+      <c r="C68" t="s">
         <v>1102</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>760</v>
-      </c>
-      <c r="B67" t="s">
-        <v>935</v>
-      </c>
-      <c r="C67" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>763</v>
+      </c>
+      <c r="B69" t="s">
+        <v>936</v>
+      </c>
+      <c r="C69" t="s">
         <v>1103</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>761</v>
-      </c>
-      <c r="B68" t="s">
-        <v>936</v>
-      </c>
-      <c r="C68" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>764</v>
+      </c>
+      <c r="B70" t="s">
+        <v>937</v>
+      </c>
+      <c r="C70" t="s">
         <v>1104</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>762</v>
-      </c>
-      <c r="B69" t="s">
-        <v>937</v>
-      </c>
-      <c r="C69" t="s">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>765</v>
+      </c>
+      <c r="B71" t="s">
+        <v>938</v>
+      </c>
+      <c r="C71" t="s">
         <v>1105</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>763</v>
-      </c>
-      <c r="B70" t="s">
-        <v>938</v>
-      </c>
-      <c r="C70" t="s">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A72" t="s">
+        <v>766</v>
+      </c>
+      <c r="B72" t="s">
+        <v>939</v>
+      </c>
+      <c r="C72" t="s">
         <v>1106</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>764</v>
-      </c>
-      <c r="B71" t="s">
-        <v>939</v>
-      </c>
-      <c r="C71" t="s">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>767</v>
+      </c>
+      <c r="B73" t="s">
+        <v>940</v>
+      </c>
+      <c r="C73" t="s">
         <v>1107</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>765</v>
-      </c>
-      <c r="B72" t="s">
-        <v>940</v>
-      </c>
-      <c r="C72" t="s">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>768</v>
+      </c>
+      <c r="B74" t="s">
+        <v>941</v>
+      </c>
+      <c r="C74" t="s">
         <v>1108</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>766</v>
-      </c>
-      <c r="B73" t="s">
-        <v>941</v>
-      </c>
-      <c r="C73" t="s">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
+        <v>769</v>
+      </c>
+      <c r="B75" t="s">
+        <v>942</v>
+      </c>
+      <c r="C75" t="s">
         <v>1109</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>767</v>
-      </c>
-      <c r="B74" t="s">
-        <v>942</v>
-      </c>
-      <c r="C74" t="s">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A76" t="s">
+        <v>770</v>
+      </c>
+      <c r="B76" t="s">
+        <v>943</v>
+      </c>
+      <c r="C76" t="s">
         <v>1110</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>768</v>
-      </c>
-      <c r="B75" t="s">
-        <v>943</v>
-      </c>
-      <c r="C75" t="s">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A77" t="s">
+        <v>771</v>
+      </c>
+      <c r="B77" t="s">
+        <v>944</v>
+      </c>
+      <c r="C77" t="s">
         <v>1111</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>769</v>
-      </c>
-      <c r="B76" t="s">
-        <v>944</v>
-      </c>
-      <c r="C76" t="s">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A78" t="s">
+        <v>772</v>
+      </c>
+      <c r="B78" t="s">
+        <v>945</v>
+      </c>
+      <c r="C78" t="s">
         <v>1112</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>770</v>
-      </c>
-      <c r="B77" t="s">
-        <v>945</v>
-      </c>
-      <c r="C77" t="s">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A79" t="s">
+        <v>773</v>
+      </c>
+      <c r="B79" t="s">
+        <v>946</v>
+      </c>
+      <c r="C79" t="s">
         <v>1113</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>771</v>
-      </c>
-      <c r="B78" t="s">
-        <v>946</v>
-      </c>
-      <c r="C78" t="s">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A80" t="s">
+        <v>774</v>
+      </c>
+      <c r="B80" t="s">
+        <v>947</v>
+      </c>
+      <c r="C80" t="s">
         <v>1114</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>772</v>
-      </c>
-      <c r="B79" t="s">
-        <v>947</v>
-      </c>
-      <c r="C79" t="s">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A81" t="s">
+        <v>775</v>
+      </c>
+      <c r="B81" t="s">
+        <v>948</v>
+      </c>
+      <c r="C81" t="s">
         <v>1115</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>773</v>
-      </c>
-      <c r="B80" t="s">
-        <v>948</v>
-      </c>
-      <c r="C80" t="s">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A82" t="s">
+        <v>776</v>
+      </c>
+      <c r="B82" t="s">
+        <v>949</v>
+      </c>
+      <c r="C82" t="s">
         <v>1116</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>774</v>
-      </c>
-      <c r="B81" t="s">
-        <v>949</v>
-      </c>
-      <c r="C81" t="s">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A83" t="s">
+        <v>777</v>
+      </c>
+      <c r="B83" t="s">
+        <v>950</v>
+      </c>
+      <c r="C83" t="s">
         <v>1117</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>775</v>
-      </c>
-      <c r="B82" t="s">
-        <v>950</v>
-      </c>
-      <c r="C82" t="s">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A84" t="s">
+        <v>778</v>
+      </c>
+      <c r="B84" t="s">
+        <v>951</v>
+      </c>
+      <c r="C84" t="s">
         <v>1118</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>776</v>
-      </c>
-      <c r="B83" t="s">
-        <v>951</v>
-      </c>
-      <c r="C83" t="s">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A85" t="s">
+        <v>779</v>
+      </c>
+      <c r="B85" t="s">
+        <v>952</v>
+      </c>
+      <c r="C85" t="s">
         <v>1119</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>777</v>
-      </c>
-      <c r="B84" t="s">
-        <v>952</v>
-      </c>
-      <c r="C84" t="s">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A86" t="s">
+        <v>780</v>
+      </c>
+      <c r="B86" t="s">
+        <v>953</v>
+      </c>
+      <c r="C86" t="s">
         <v>1120</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>778</v>
-      </c>
-      <c r="B85" t="s">
-        <v>953</v>
-      </c>
-      <c r="C85" t="s">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A87" t="s">
+        <v>781</v>
+      </c>
+      <c r="B87" t="s">
+        <v>954</v>
+      </c>
+      <c r="C87" t="s">
         <v>1121</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>779</v>
-      </c>
-      <c r="B86" t="s">
-        <v>954</v>
-      </c>
-      <c r="C86" t="s">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A88" t="s">
+        <v>782</v>
+      </c>
+      <c r="B88" t="s">
+        <v>955</v>
+      </c>
+      <c r="C88" t="s">
         <v>1122</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>780</v>
-      </c>
-      <c r="B87" t="s">
-        <v>955</v>
-      </c>
-      <c r="C87" t="s">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A89" t="s">
+        <v>783</v>
+      </c>
+      <c r="B89" t="s">
+        <v>956</v>
+      </c>
+      <c r="C89" t="s">
         <v>1123</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>781</v>
-      </c>
-      <c r="B88" t="s">
-        <v>956</v>
-      </c>
-      <c r="C88" t="s">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A90" t="s">
+        <v>784</v>
+      </c>
+      <c r="B90" t="s">
+        <v>957</v>
+      </c>
+      <c r="C90" t="s">
         <v>1124</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>782</v>
-      </c>
-      <c r="B89" t="s">
-        <v>957</v>
-      </c>
-      <c r="C89" t="s">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A91" t="s">
+        <v>785</v>
+      </c>
+      <c r="B91" t="s">
+        <v>958</v>
+      </c>
+      <c r="C91" t="s">
         <v>1125</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>783</v>
-      </c>
-      <c r="B90" t="s">
-        <v>958</v>
-      </c>
-      <c r="C90" t="s">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A92" t="s">
+        <v>786</v>
+      </c>
+      <c r="B92" t="s">
+        <v>959</v>
+      </c>
+      <c r="C92" t="s">
         <v>1126</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>784</v>
-      </c>
-      <c r="B91" t="s">
-        <v>959</v>
-      </c>
-      <c r="C91" t="s">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A93" t="s">
+        <v>787</v>
+      </c>
+      <c r="B93" t="s">
+        <v>960</v>
+      </c>
+      <c r="C93" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
-        <v>785</v>
-      </c>
-      <c r="B92" t="s">
-        <v>960</v>
-      </c>
-      <c r="C92" t="s">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A94" t="s">
+        <v>788</v>
+      </c>
+      <c r="B94" t="s">
+        <v>961</v>
+      </c>
+      <c r="C94" t="s">
         <v>1128</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>786</v>
-      </c>
-      <c r="B93" t="s">
-        <v>961</v>
-      </c>
-      <c r="C93" t="s">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A95" t="s">
+        <v>789</v>
+      </c>
+      <c r="B95" t="s">
+        <v>962</v>
+      </c>
+      <c r="C95" t="s">
         <v>1129</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>787</v>
-      </c>
-      <c r="B94" t="s">
-        <v>962</v>
-      </c>
-      <c r="C94" t="s">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A96" t="s">
+        <v>790</v>
+      </c>
+      <c r="B96" t="s">
+        <v>963</v>
+      </c>
+      <c r="C96" t="s">
         <v>1130</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>788</v>
-      </c>
-      <c r="B95" t="s">
-        <v>963</v>
-      </c>
-      <c r="C95" t="s">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A97" t="s">
+        <v>791</v>
+      </c>
+      <c r="B97" t="s">
+        <v>964</v>
+      </c>
+      <c r="C97" t="s">
         <v>1131</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>789</v>
-      </c>
-      <c r="B96" t="s">
-        <v>964</v>
-      </c>
-      <c r="C96" t="s">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A98" t="s">
+        <v>792</v>
+      </c>
+      <c r="B98" t="s">
+        <v>965</v>
+      </c>
+      <c r="C98" t="s">
         <v>1132</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>790</v>
-      </c>
-      <c r="B97" t="s">
-        <v>965</v>
-      </c>
-      <c r="C97" t="s">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A99" t="s">
+        <v>793</v>
+      </c>
+      <c r="B99" t="s">
+        <v>966</v>
+      </c>
+      <c r="C99" t="s">
         <v>1133</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>791</v>
-      </c>
-      <c r="B98" t="s">
-        <v>966</v>
-      </c>
-      <c r="C98" t="s">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A100" t="s">
+        <v>794</v>
+      </c>
+      <c r="B100" t="s">
+        <v>967</v>
+      </c>
+      <c r="C100" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>792</v>
-      </c>
-      <c r="B99" t="s">
-        <v>967</v>
-      </c>
-      <c r="C99" t="s">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A101" t="s">
+        <v>795</v>
+      </c>
+      <c r="B101" t="s">
+        <v>968</v>
+      </c>
+      <c r="C101" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>793</v>
-      </c>
-      <c r="B100" t="s">
-        <v>968</v>
-      </c>
-      <c r="C100" t="s">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A102" t="s">
+        <v>796</v>
+      </c>
+      <c r="B102" t="s">
+        <v>969</v>
+      </c>
+      <c r="C102" t="s">
         <v>1136</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>794</v>
-      </c>
-      <c r="B101" t="s">
-        <v>969</v>
-      </c>
-      <c r="C101" t="s">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A103" t="s">
+        <v>797</v>
+      </c>
+      <c r="B103" t="s">
+        <v>970</v>
+      </c>
+      <c r="C103" t="s">
         <v>1137</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>795</v>
-      </c>
-      <c r="B102" t="s">
-        <v>970</v>
-      </c>
-      <c r="C102" t="s">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A104" t="s">
+        <v>798</v>
+      </c>
+      <c r="B104" t="s">
+        <v>971</v>
+      </c>
+      <c r="C104" t="s">
         <v>1138</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>796</v>
-      </c>
-      <c r="B103" t="s">
-        <v>971</v>
-      </c>
-      <c r="C103" t="s">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A105" t="s">
+        <v>799</v>
+      </c>
+      <c r="B105" t="s">
+        <v>972</v>
+      </c>
+      <c r="C105" t="s">
         <v>1139</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>797</v>
-      </c>
-      <c r="B104" t="s">
-        <v>972</v>
-      </c>
-      <c r="C104" t="s">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A106" t="s">
+        <v>800</v>
+      </c>
+      <c r="B106" t="s">
+        <v>973</v>
+      </c>
+      <c r="C106" t="s">
         <v>1140</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>798</v>
-      </c>
-      <c r="B105" t="s">
-        <v>973</v>
-      </c>
-      <c r="C105" t="s">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A107" t="s">
+        <v>801</v>
+      </c>
+      <c r="B107" t="s">
+        <v>974</v>
+      </c>
+      <c r="C107" t="s">
         <v>1141</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>799</v>
-      </c>
-      <c r="B106" t="s">
-        <v>974</v>
-      </c>
-      <c r="C106" t="s">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A108" t="s">
+        <v>802</v>
+      </c>
+      <c r="B108" t="s">
+        <v>975</v>
+      </c>
+      <c r="C108" t="s">
         <v>1142</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>800</v>
-      </c>
-      <c r="B107" t="s">
-        <v>975</v>
-      </c>
-      <c r="C107" t="s">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A109" t="s">
+        <v>803</v>
+      </c>
+      <c r="B109" t="s">
+        <v>976</v>
+      </c>
+      <c r="C109" t="s">
         <v>1143</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>801</v>
-      </c>
-      <c r="B108" t="s">
-        <v>976</v>
-      </c>
-      <c r="C108" t="s">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A110" t="s">
+        <v>804</v>
+      </c>
+      <c r="B110" t="s">
+        <v>977</v>
+      </c>
+      <c r="C110" t="s">
         <v>1144</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>802</v>
-      </c>
-      <c r="B109" t="s">
-        <v>977</v>
-      </c>
-      <c r="C109" t="s">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A111" t="s">
+        <v>805</v>
+      </c>
+      <c r="B111" t="s">
+        <v>978</v>
+      </c>
+      <c r="C111" t="s">
         <v>1145</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>803</v>
-      </c>
-      <c r="B110" t="s">
-        <v>978</v>
-      </c>
-      <c r="C110" t="s">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A112" t="s">
+        <v>806</v>
+      </c>
+      <c r="B112" t="s">
+        <v>979</v>
+      </c>
+      <c r="C112" t="s">
         <v>1146</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>804</v>
-      </c>
-      <c r="B111" t="s">
-        <v>979</v>
-      </c>
-      <c r="C111" t="s">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A113" t="s">
+        <v>807</v>
+      </c>
+      <c r="B113" t="s">
+        <v>980</v>
+      </c>
+      <c r="C113" t="s">
         <v>1147</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>805</v>
-      </c>
-      <c r="B112" t="s">
-        <v>980</v>
-      </c>
-      <c r="C112" t="s">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A114" t="s">
+        <v>808</v>
+      </c>
+      <c r="B114" t="s">
+        <v>981</v>
+      </c>
+      <c r="C114" t="s">
         <v>1148</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
-        <v>806</v>
-      </c>
-      <c r="B113" t="s">
-        <v>981</v>
-      </c>
-      <c r="C113" t="s">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A115" t="s">
+        <v>809</v>
+      </c>
+      <c r="B115" t="s">
+        <v>982</v>
+      </c>
+      <c r="C115" t="s">
         <v>1149</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>807</v>
-      </c>
-      <c r="B114" t="s">
-        <v>982</v>
-      </c>
-      <c r="C114" t="s">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A116" t="s">
+        <v>810</v>
+      </c>
+      <c r="B116" t="s">
+        <v>983</v>
+      </c>
+      <c r="C116" t="s">
         <v>1150</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>808</v>
-      </c>
-      <c r="B115" t="s">
-        <v>983</v>
-      </c>
-      <c r="C115" t="s">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A117" t="s">
+        <v>811</v>
+      </c>
+      <c r="B117" t="s">
+        <v>984</v>
+      </c>
+      <c r="C117" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>809</v>
-      </c>
-      <c r="B116" t="s">
-        <v>984</v>
-      </c>
-      <c r="C116" t="s">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A118" t="s">
+        <v>812</v>
+      </c>
+      <c r="B118" t="s">
+        <v>985</v>
+      </c>
+      <c r="C118" t="s">
         <v>1152</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>810</v>
-      </c>
-      <c r="B117" t="s">
-        <v>985</v>
-      </c>
-      <c r="C117" t="s">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A119" t="s">
+        <v>813</v>
+      </c>
+      <c r="B119" t="s">
+        <v>986</v>
+      </c>
+      <c r="C119" t="s">
         <v>1153</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
-        <v>811</v>
-      </c>
-      <c r="B118" t="s">
-        <v>986</v>
-      </c>
-      <c r="C118" t="s">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A120" t="s">
+        <v>814</v>
+      </c>
+      <c r="B120" t="s">
+        <v>987</v>
+      </c>
+      <c r="C120" t="s">
         <v>1154</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
-        <v>812</v>
-      </c>
-      <c r="B119" t="s">
-        <v>987</v>
-      </c>
-      <c r="C119" t="s">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A121" t="s">
+        <v>815</v>
+      </c>
+      <c r="B121" t="s">
+        <v>988</v>
+      </c>
+      <c r="C121" t="s">
         <v>1155</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
-        <v>813</v>
-      </c>
-      <c r="B120" t="s">
-        <v>988</v>
-      </c>
-      <c r="C120" t="s">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A122" t="s">
+        <v>816</v>
+      </c>
+      <c r="B122" t="s">
+        <v>989</v>
+      </c>
+      <c r="C122" t="s">
         <v>1156</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
-        <v>814</v>
-      </c>
-      <c r="B121" t="s">
-        <v>989</v>
-      </c>
-      <c r="C121" t="s">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A123" t="s">
+        <v>817</v>
+      </c>
+      <c r="B123" t="s">
+        <v>990</v>
+      </c>
+      <c r="C123" t="s">
         <v>1157</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
-        <v>815</v>
-      </c>
-      <c r="B122" t="s">
-        <v>990</v>
-      </c>
-      <c r="C122" t="s">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A124" t="s">
+        <v>818</v>
+      </c>
+      <c r="B124" t="s">
+        <v>991</v>
+      </c>
+      <c r="C124" t="s">
         <v>1158</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
-        <v>816</v>
-      </c>
-      <c r="B123" t="s">
-        <v>991</v>
-      </c>
-      <c r="C123" t="s">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A125" t="s">
+        <v>819</v>
+      </c>
+      <c r="B125" t="s">
+        <v>992</v>
+      </c>
+      <c r="C125" t="s">
         <v>1159</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
-        <v>817</v>
-      </c>
-      <c r="B124" t="s">
-        <v>992</v>
-      </c>
-      <c r="C124" t="s">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A126" t="s">
+        <v>820</v>
+      </c>
+      <c r="B126" t="s">
+        <v>993</v>
+      </c>
+      <c r="C126" t="s">
         <v>1160</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
-        <v>818</v>
-      </c>
-      <c r="B125" t="s">
-        <v>993</v>
-      </c>
-      <c r="C125" t="s">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A127" t="s">
+        <v>821</v>
+      </c>
+      <c r="B127" t="s">
+        <v>994</v>
+      </c>
+      <c r="C127" t="s">
         <v>1161</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
-        <v>819</v>
-      </c>
-      <c r="B126" t="s">
-        <v>994</v>
-      </c>
-      <c r="C126" t="s">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A128" t="s">
+        <v>822</v>
+      </c>
+      <c r="B128" t="s">
+        <v>995</v>
+      </c>
+      <c r="C128" t="s">
         <v>1162</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
-        <v>820</v>
-      </c>
-      <c r="B127" t="s">
-        <v>995</v>
-      </c>
-      <c r="C127" t="s">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A129" t="s">
+        <v>823</v>
+      </c>
+      <c r="B129" t="s">
+        <v>996</v>
+      </c>
+      <c r="C129" t="s">
         <v>1163</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
-        <v>821</v>
-      </c>
-      <c r="B128" t="s">
-        <v>996</v>
-      </c>
-      <c r="C128" t="s">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A130" t="s">
+        <v>824</v>
+      </c>
+      <c r="B130" t="s">
+        <v>997</v>
+      </c>
+      <c r="C130" t="s">
         <v>1164</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
-        <v>822</v>
-      </c>
-      <c r="B129" t="s">
-        <v>997</v>
-      </c>
-      <c r="C129" t="s">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A131" t="s">
+        <v>825</v>
+      </c>
+      <c r="B131" t="s">
+        <v>998</v>
+      </c>
+      <c r="C131" t="s">
         <v>1165</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
-        <v>823</v>
-      </c>
-      <c r="B130" t="s">
-        <v>998</v>
-      </c>
-      <c r="C130" t="s">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A132" t="s">
+        <v>826</v>
+      </c>
+      <c r="B132" t="s">
+        <v>999</v>
+      </c>
+      <c r="C132" t="s">
         <v>1166</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
-        <v>824</v>
-      </c>
-      <c r="B131" t="s">
-        <v>999</v>
-      </c>
-      <c r="C131" t="s">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A133" t="s">
+        <v>827</v>
+      </c>
+      <c r="B133" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C133" t="s">
         <v>1167</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
-        <v>825</v>
-      </c>
-      <c r="B132" t="s">
-        <v>1000</v>
-      </c>
-      <c r="C132" t="s">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A134" t="s">
+        <v>828</v>
+      </c>
+      <c r="B134" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C134" t="s">
         <v>1168</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
-        <v>826</v>
-      </c>
-      <c r="B133" t="s">
-        <v>1001</v>
-      </c>
-      <c r="C133" t="s">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A135" t="s">
+        <v>829</v>
+      </c>
+      <c r="B135" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C135" t="s">
         <v>1169</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
-        <v>827</v>
-      </c>
-      <c r="B134" t="s">
-        <v>1002</v>
-      </c>
-      <c r="C134" t="s">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A136" t="s">
+        <v>830</v>
+      </c>
+      <c r="B136" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C136" t="s">
         <v>1170</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
-        <v>828</v>
-      </c>
-      <c r="B135" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C135" t="s">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A137" t="s">
+        <v>831</v>
+      </c>
+      <c r="B137" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C137" t="s">
         <v>1171</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
-        <v>829</v>
-      </c>
-      <c r="B136" t="s">
-        <v>1004</v>
-      </c>
-      <c r="C136" t="s">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A138" t="s">
+        <v>832</v>
+      </c>
+      <c r="B138" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C138" t="s">
         <v>1172</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
-        <v>830</v>
-      </c>
-      <c r="B137" t="s">
-        <v>1005</v>
-      </c>
-      <c r="C137" t="s">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A139" t="s">
+        <v>833</v>
+      </c>
+      <c r="B139" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C139" t="s">
         <v>1173</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
-        <v>831</v>
-      </c>
-      <c r="B138" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C138" t="s">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A140" t="s">
+        <v>834</v>
+      </c>
+      <c r="B140" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C140" t="s">
         <v>1174</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
-        <v>832</v>
-      </c>
-      <c r="B139" t="s">
-        <v>1007</v>
-      </c>
-      <c r="C139" t="s">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A141" t="s">
+        <v>835</v>
+      </c>
+      <c r="B141" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C141" t="s">
         <v>1175</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
-        <v>833</v>
-      </c>
-      <c r="B140" t="s">
-        <v>1008</v>
-      </c>
-      <c r="C140" t="s">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A142" t="s">
+        <v>836</v>
+      </c>
+      <c r="B142" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C142" t="s">
         <v>1176</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
-        <v>834</v>
-      </c>
-      <c r="B141" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C141" t="s">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A143" t="s">
+        <v>837</v>
+      </c>
+      <c r="B143" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C143" t="s">
         <v>1177</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
-        <v>835</v>
-      </c>
-      <c r="B142" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C142" t="s">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A144" t="s">
+        <v>838</v>
+      </c>
+      <c r="B144" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C144" t="s">
         <v>1178</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
-        <v>836</v>
-      </c>
-      <c r="B143" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C143" t="s">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A145" t="s">
+        <v>839</v>
+      </c>
+      <c r="B145" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C145" t="s">
         <v>1179</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
-        <v>837</v>
-      </c>
-      <c r="B144" t="s">
-        <v>1012</v>
-      </c>
-      <c r="C144" t="s">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A146" t="s">
+        <v>840</v>
+      </c>
+      <c r="B146" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C146" t="s">
         <v>1180</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A145" t="s">
-        <v>838</v>
-      </c>
-      <c r="B145" t="s">
-        <v>1013</v>
-      </c>
-      <c r="C145" t="s">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A147" t="s">
+        <v>841</v>
+      </c>
+      <c r="B147" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C147" t="s">
         <v>1181</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A146" t="s">
-        <v>839</v>
-      </c>
-      <c r="B146" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C146" t="s">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A148" t="s">
+        <v>842</v>
+      </c>
+      <c r="B148" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C148" t="s">
         <v>1182</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A147" t="s">
-        <v>840</v>
-      </c>
-      <c r="B147" t="s">
-        <v>1015</v>
-      </c>
-      <c r="C147" t="s">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A149" t="s">
+        <v>843</v>
+      </c>
+      <c r="B149" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C149" t="s">
         <v>1183</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A148" t="s">
-        <v>841</v>
-      </c>
-      <c r="B148" t="s">
-        <v>1016</v>
-      </c>
-      <c r="C148" t="s">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A150" t="s">
+        <v>844</v>
+      </c>
+      <c r="B150" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C150" t="s">
         <v>1184</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A149" t="s">
-        <v>842</v>
-      </c>
-      <c r="B149" t="s">
-        <v>1017</v>
-      </c>
-      <c r="C149" t="s">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A151" t="s">
+        <v>845</v>
+      </c>
+      <c r="B151" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C151" t="s">
         <v>1185</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
-        <v>843</v>
-      </c>
-      <c r="B150" t="s">
-        <v>1018</v>
-      </c>
-      <c r="C150" t="s">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A152" t="s">
+        <v>846</v>
+      </c>
+      <c r="B152" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C152" t="s">
         <v>1186</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
-        <v>844</v>
-      </c>
-      <c r="B151" t="s">
-        <v>1019</v>
-      </c>
-      <c r="C151" t="s">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A153" t="s">
+        <v>847</v>
+      </c>
+      <c r="B153" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C153" t="s">
         <v>1187</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A152" t="s">
-        <v>845</v>
-      </c>
-      <c r="B152" t="s">
-        <v>1020</v>
-      </c>
-      <c r="C152" t="s">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A154" t="s">
+        <v>848</v>
+      </c>
+      <c r="B154" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C154" t="s">
         <v>1188</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A153" t="s">
-        <v>846</v>
-      </c>
-      <c r="B153" t="s">
-        <v>1021</v>
-      </c>
-      <c r="C153" t="s">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A155" t="s">
+        <v>849</v>
+      </c>
+      <c r="B155" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C155" t="s">
         <v>1189</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A154" t="s">
-        <v>847</v>
-      </c>
-      <c r="B154" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C154" t="s">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A156" t="s">
+        <v>850</v>
+      </c>
+      <c r="B156" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C156" t="s">
         <v>1190</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A155" t="s">
-        <v>848</v>
-      </c>
-      <c r="B155" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C155" t="s">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A157" t="s">
+        <v>851</v>
+      </c>
+      <c r="B157" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C157" t="s">
         <v>1191</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
-        <v>849</v>
-      </c>
-      <c r="B156" t="s">
-        <v>1024</v>
-      </c>
-      <c r="C156" t="s">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A158" t="s">
+        <v>852</v>
+      </c>
+      <c r="B158" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C158" t="s">
         <v>1192</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A157" t="s">
-        <v>850</v>
-      </c>
-      <c r="B157" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C157" t="s">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A159" t="s">
+        <v>853</v>
+      </c>
+      <c r="B159" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C159" t="s">
         <v>1193</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A158" t="s">
-        <v>851</v>
-      </c>
-      <c r="B158" t="s">
-        <v>1026</v>
-      </c>
-      <c r="C158" t="s">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A160" t="s">
+        <v>854</v>
+      </c>
+      <c r="B160" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C160" t="s">
         <v>1194</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A159" t="s">
-        <v>852</v>
-      </c>
-      <c r="B159" t="s">
-        <v>1027</v>
-      </c>
-      <c r="C159" t="s">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A161" t="s">
+        <v>855</v>
+      </c>
+      <c r="B161" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C161" t="s">
         <v>1195</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A160" t="s">
-        <v>853</v>
-      </c>
-      <c r="B160" t="s">
-        <v>1028</v>
-      </c>
-      <c r="C160" t="s">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A162" t="s">
+        <v>856</v>
+      </c>
+      <c r="B162" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C162" t="s">
         <v>1196</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A161" t="s">
-        <v>854</v>
-      </c>
-      <c r="B161" t="s">
-        <v>1029</v>
-      </c>
-      <c r="C161" t="s">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A163" t="s">
+        <v>857</v>
+      </c>
+      <c r="B163" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C163" t="s">
         <v>1197</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A162" t="s">
-        <v>855</v>
-      </c>
-      <c r="B162" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C162" t="s">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A164" t="s">
+        <v>858</v>
+      </c>
+      <c r="B164" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C164" t="s">
         <v>1198</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A163" t="s">
-        <v>856</v>
-      </c>
-      <c r="B163" t="s">
-        <v>1031</v>
-      </c>
-      <c r="C163" t="s">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A165" t="s">
+        <v>859</v>
+      </c>
+      <c r="B165" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C165" t="s">
         <v>1199</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A164" t="s">
-        <v>857</v>
-      </c>
-      <c r="B164" t="s">
-        <v>1032</v>
-      </c>
-      <c r="C164" t="s">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A166" t="s">
+        <v>860</v>
+      </c>
+      <c r="B166" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C166" t="s">
         <v>1200</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A165" t="s">
-        <v>858</v>
-      </c>
-      <c r="B165" t="s">
-        <v>1033</v>
-      </c>
-      <c r="C165" t="s">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A167" t="s">
+        <v>861</v>
+      </c>
+      <c r="B167" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C167" t="s">
         <v>1201</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A166" t="s">
-        <v>859</v>
-      </c>
-      <c r="B166" t="s">
-        <v>1034</v>
-      </c>
-      <c r="C166" t="s">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A168" t="s">
+        <v>862</v>
+      </c>
+      <c r="B168" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C168" t="s">
         <v>1202</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A167" t="s">
-        <v>860</v>
-      </c>
-      <c r="B167" t="s">
-        <v>1035</v>
-      </c>
-      <c r="C167" t="s">
-        <v>1203</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A168" t="s">
-        <v>861</v>
-      </c>
-      <c r="B168" t="s">
-        <v>1036</v>
-      </c>
-      <c r="C168" t="s">
-        <v>1204</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A169" t="s">
-        <v>862</v>
-      </c>
-      <c r="B169" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C169" t="s">
-        <v>1205</v>
       </c>
     </row>
   </sheetData>
